--- a/output/pdf_financials_xlsx/ETG.xlsx
+++ b/output/pdf_financials_xlsx/ETG.xlsx
@@ -1195,22 +1195,22 @@
         <v>5.524</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>7.555</v>
+        <v>-7.555</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>9.061</v>
+        <v>-9.061</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>9.579000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>14.321</v>
+        <v>-14.321</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>12.199</v>
+        <v>-12.199</v>
       </c>
     </row>
     <row r="17">
@@ -1226,22 +1226,22 @@
         <v>2.062756</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-4.057</v>
+        <v>-21.395</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>3.871</v>
+        <v>-11.791</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.912</v>
+        <v>-8.414</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.104</v>
+        <v>-73.126</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>-10.396</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>-11.048</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-0</v>
@@ -1429,40 +1429,40 @@
         <v>-11.422025</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8.669</v>
+        <v>-8.669</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7.831</v>
+        <v>-7.831</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.663</v>
+        <v>-4.663</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>36.615</v>
+        <v>-36.615</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.198</v>
+        <v>-5.198</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.524</v>
+        <v>-5.524</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>7.555</v>
+        <v>-7.555</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>9.061</v>
+        <v>-9.061</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>9.579000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>14.321</v>
+        <v>-14.321</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>12.199</v>
+        <v>-12.199</v>
       </c>
     </row>
     <row r="21">
@@ -1576,40 +1576,40 @@
         <v>-11.422025</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>8.669</v>
+        <v>-8.669</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7.831</v>
+        <v>-7.831</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.663</v>
+        <v>-4.663</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>36.615</v>
+        <v>-36.615</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.198</v>
+        <v>-5.198</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>5.524</v>
+        <v>-5.524</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.555</v>
+        <v>-7.555</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>9.061</v>
+        <v>-9.061</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>9.579000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>14.321</v>
+        <v>-14.321</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>12.199</v>
+        <v>-12.199</v>
       </c>
     </row>
     <row r="24">
@@ -1807,16 +1807,16 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-181.22</v>
+        <v>181.22</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-191.58</v>
+        <v>191.58</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-204.585714</v>
+        <v>204.585714</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>-203.316667</v>
+        <v>203.316667</v>
       </c>
     </row>
     <row r="27">
@@ -1850,22 +1850,22 @@
         <v>5.524</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.555</v>
+        <v>-7.555</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>9.061</v>
+        <v>-9.061</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>9.579000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>14.321</v>
+        <v>-14.321</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>12.199</v>
+        <v>-12.199</v>
       </c>
     </row>
     <row r="28">
@@ -1948,22 +1948,22 @@
         <v>5.629</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>6.098</v>
+        <v>-5.902</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>7.673</v>
+        <v>-7.437</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>9.185</v>
+        <v>-8.936999999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>9.694000000000001</v>
+        <v>-9.464</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>14.439</v>
+        <v>-14.203</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>12.312</v>
+        <v>-12.086</v>
       </c>
     </row>
     <row r="30">
@@ -2056,40 +2056,40 @@
         <v>-15.29691880053521</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>31.87961653308188</v>
+        <v>168.1203834669181</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>97.75252525252526</v>
+        <v>297.7525252525253</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>24.31351639562783</v>
+        <v>224.3135163956279</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2848456629508915</v>
+        <v>200.2848456629509</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5318,13 +5318,13 @@
         <v>20.863</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>22.175</v>
+        <v>20.863</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>22.199</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>22.445</v>
       </c>
       <c r="J92" s="1" t="inlineStr">
         <is>
@@ -5332,19 +5332,19 @@
         </is>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>22.728</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>22.509</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>22.269</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>23.252</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>24.575</v>
       </c>
     </row>
     <row r="93">
@@ -5641,13 +5641,13 @@
         <v>-4.663</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>36.615</v>
+        <v>-36.615</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>5.198</v>
+        <v>-5.198</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>5.524</v>
+        <v>-5.524</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>-6</v>
@@ -9016,7 +9016,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
           <t>-</t>
@@ -12112,7 +12116,11 @@
           <t>Reserves 22,199</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -33686,22 +33694,22 @@
         </is>
       </c>
       <c r="M313" s="5" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="N313" s="5" t="n">
-        <v>7.555</v>
+        <v>-7.555</v>
       </c>
       <c r="O313" s="5" t="n">
-        <v>9.061</v>
+        <v>-9.061</v>
       </c>
       <c r="P313" s="5" t="n">
-        <v>9.579000000000001</v>
+        <v>-9.579000000000001</v>
       </c>
       <c r="Q313" s="5" t="n">
-        <v>14.321</v>
+        <v>-14.321</v>
       </c>
       <c r="R313" s="5" t="n">
-        <v>12.199</v>
+        <v>-12.199</v>
       </c>
     </row>
     <row r="314">
@@ -40543,13 +40551,13 @@
         </is>
       </c>
       <c r="J395" s="5" t="n">
-        <v>36.615</v>
+        <v>-36.615</v>
       </c>
       <c r="K395" s="5" t="n">
-        <v>5.198</v>
+        <v>-5.198</v>
       </c>
       <c r="L395" s="5" t="n">
-        <v>5.524</v>
+        <v>-5.524</v>
       </c>
       <c r="M395" t="inlineStr">
         <is>
@@ -43171,10 +43179,10 @@
         </is>
       </c>
       <c r="J426" s="5" t="n">
-        <v>38.299</v>
+        <v>-38.299</v>
       </c>
       <c r="K426" s="5" t="n">
-        <v>1.826</v>
+        <v>-1.826</v>
       </c>
       <c r="L426" t="inlineStr">
         <is>
@@ -45283,13 +45291,13 @@
         </is>
       </c>
       <c r="H451" s="5" t="n">
-        <v>7.831</v>
+        <v>-7.831</v>
       </c>
       <c r="I451" s="5" t="n">
-        <v>4.663</v>
+        <v>-4.663</v>
       </c>
       <c r="J451" s="5" t="n">
-        <v>3.199</v>
+        <v>-3.199</v>
       </c>
       <c r="K451" t="inlineStr">
         <is>
@@ -45449,13 +45457,13 @@
         </is>
       </c>
       <c r="H453" s="5" t="n">
-        <v>12.759</v>
+        <v>-12.759</v>
       </c>
       <c r="I453" s="5" t="n">
-        <v>3.946</v>
+        <v>-3.946</v>
       </c>
       <c r="J453" s="5" t="n">
-        <v>5.68</v>
+        <v>-5.68</v>
       </c>
       <c r="K453" t="inlineStr">
         <is>
@@ -46618,13 +46626,13 @@
         </is>
       </c>
       <c r="G467" s="5" t="n">
-        <v>8.669</v>
+        <v>-8.669</v>
       </c>
       <c r="H467" s="5" t="n">
-        <v>7.831</v>
+        <v>-7.831</v>
       </c>
       <c r="I467" s="5" t="n">
-        <v>4.663</v>
+        <v>-4.663</v>
       </c>
       <c r="J467" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ETG.xlsx
+++ b/output/pdf_financials_xlsx/ETG.xlsx
@@ -975,46 +975,46 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.190449</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.431596</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.295</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.102</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.116</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.111</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.137</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.08</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.147</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.333</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.213</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.182</v>
       </c>
     </row>
     <row r="13">
@@ -1826,46 +1826,46 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-14.866359</v>
+        <v>-15.056808</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-13.484781</v>
+        <v>-13.916377</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>12.726</v>
+        <v>13.021</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>3.96</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>3.751</v>
+        <v>3.853</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>36.511</v>
+        <v>36.627</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.198</v>
+        <v>5.309</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.524</v>
+        <v>5.661</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-6</v>
+        <v>-5.92</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-7.555</v>
+        <v>-7.53</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-9.061</v>
+        <v>-8.914</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-9.579000000000001</v>
+        <v>-9.246</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-14.321</v>
+        <v>-14.108</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-12.199</v>
+        <v>-12.017</v>
       </c>
     </row>
     <row r="28">
@@ -1924,46 +1924,46 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-14.715705</v>
+        <v>-14.906154</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-13.38184</v>
+        <v>-13.813436</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>12.792</v>
+        <v>13.087</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>3.981</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>3.767</v>
+        <v>3.869</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>36.531</v>
+        <v>36.647</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.22</v>
+        <v>5.331</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>5.629</v>
+        <v>5.766</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-5.902</v>
+        <v>-5.822</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-7.437</v>
+        <v>-7.412</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-8.936999999999999</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-9.464</v>
+        <v>-9.131</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-14.203</v>
+        <v>-13.99</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-12.086</v>
+        <v>-11.904</v>
       </c>
     </row>
     <row r="30">
@@ -19058,7 +19058,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -29340,7 +29344,11 @@
           <t>Gain on release of reclamation deposits</t>
         </is>
       </c>
-      <c r="D261" t="inlineStr"/>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E261" t="inlineStr">
         <is>
           <t>-</t>
@@ -29852,7 +29860,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D267" t="inlineStr"/>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -31808,7 +31820,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D290" t="inlineStr"/>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E290" s="5" t="n">
         <v>-0.207962</v>
       </c>
@@ -33274,7 +33290,7 @@
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
@@ -33344,7 +33360,7 @@
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
@@ -39682,7 +39698,7 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -42806,7 +42822,7 @@
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
@@ -44854,7 +44870,7 @@
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E446" t="inlineStr">
@@ -46362,7 +46378,7 @@
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
@@ -47618,7 +47634,7 @@
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E479" s="5" t="n">
@@ -47704,7 +47720,7 @@
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E480" s="5" t="n">

--- a/output/pdf_financials_xlsx/ETG.xlsx
+++ b/output/pdf_financials_xlsx/ETG.xlsx
@@ -1220,22 +1220,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.32977</v>
+        <v>0.32977</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>2.062756</v>
+        <v>0.319112</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-21.395</v>
+        <v>4.057</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-11.791</v>
+        <v>-0.16</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-8.414</v>
+        <v>0.553</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-73.126</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-10.396</v>
@@ -1432,13 +1432,13 @@
         <v>-8.669</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-7.831</v>
+        <v>-4.12</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-4.663</v>
+        <v>-3.198</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>-36.615</v>
+        <v>-36.439</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-5.198</v>
@@ -1481,13 +1481,13 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-3.711</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0</v>
+        <v>-1.465</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>-0.176</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0</v>
@@ -2053,19 +2053,19 @@
         <v>-2.218229762916394</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>-15.29691880053521</v>
+        <v>-2.366460382263531</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>168.1203834669181</v>
+        <v>31.87961653308188</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>297.7525252525253</v>
+        <v>4.040404040404041</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>224.3135163956279</v>
+        <v>14.74273527059451</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>200.2848456629509</v>
+        <v>0.1972008435813865</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>200</v>
@@ -5635,13 +5635,13 @@
         <v>-8.669</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-7.831</v>
+        <v>-4.12</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>-4.663</v>
+        <v>-3.198</v>
       </c>
       <c r="G99" s="3" t="n">
-        <v>-36.615</v>
+        <v>-36.439</v>
       </c>
       <c r="H99" s="3" t="n">
         <v>-5.198</v>
@@ -6214,25 +6214,25 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.035893</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.007623</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="G111" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="H111" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="I111" s="3" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>0</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -6431,7 +6431,7 @@
         <v>0</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="J115" s="3" t="n">
         <v>0</v>
@@ -7379,25 +7379,25 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.035893</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.007623</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.013</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.016</v>
       </c>
       <c r="F134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="G134" s="3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="H134" s="3" t="n">
-        <v>0</v>
+        <v>-0.006</v>
       </c>
       <c r="I134" s="3" t="n">
         <v>0</v>
@@ -7406,7 +7406,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.033</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -7428,25 +7428,25 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-12.801856</v>
+        <v>-12.837749</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>27.97915</v>
+        <v>27.971527</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-12.617637</v>
+        <v>-12.630637</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-9.385999999999999</v>
+        <v>-9.401999999999999</v>
       </c>
       <c r="F135" s="3" t="n">
-        <v>-10.371</v>
+        <v>-10.377</v>
       </c>
       <c r="G135" s="3" t="n">
-        <v>-3.504</v>
+        <v>-3.604</v>
       </c>
       <c r="H135" s="3" t="n">
-        <v>-0.777</v>
+        <v>-0.783</v>
       </c>
       <c r="I135" s="3" t="n">
         <v>-1.816</v>
@@ -7457,7 +7457,7 @@
         </is>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-2.152</v>
+        <v>-2.185</v>
       </c>
       <c r="L135" s="1" t="inlineStr">
         <is>
@@ -20914,7 +20914,11 @@
           <t>Proceeds from issuance of common shares – private placement 10</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -21074,7 +21078,11 @@
           <t>Share issuance costs – private placement 10</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -22514,7 +22522,11 @@
           <t>Purchase of equipment 5</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -22862,7 +22874,11 @@
           <t>Net loss from continuing operations $</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -24188,7 +24204,11 @@
           <t>Proceeds from sale of investments 6</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -24360,7 +24380,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -24784,7 +24808,11 @@
           <t>Proceeds from issuance of common shares – private placement 13</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -26148,7 +26176,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D223" t="inlineStr"/>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E223" t="inlineStr">
         <is>
           <t>-</t>
@@ -27836,7 +27868,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -28172,7 +28208,11 @@
           <t>Proceeds from issuance of capital stock – private placement 9</t>
         </is>
       </c>
-      <c r="D247" t="inlineStr"/>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -29946,7 +29986,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -30716,7 +30760,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D277" t="inlineStr"/>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E277" s="5" t="n">
         <v>0.32977</v>
       </c>
@@ -31992,7 +32040,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D292" t="inlineStr"/>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E292" s="5" t="n">
         <v>-0.035893</v>
       </c>
@@ -40286,7 +40338,11 @@
           <t>Income tax recovery 16</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -40372,7 +40428,11 @@
           <t>Net loss from continuing operations</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
@@ -40389,19 +40449,19 @@
         </is>
       </c>
       <c r="H393" s="5" t="n">
-        <v>4.12</v>
+        <v>-4.12</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>3.198</v>
+        <v>-3.198</v>
       </c>
       <c r="J393" s="5" t="n">
-        <v>36.439</v>
+        <v>-36.439</v>
       </c>
       <c r="K393" s="5" t="n">
-        <v>5.198</v>
+        <v>-5.198</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>5.524</v>
+        <v>-5.524</v>
       </c>
       <c r="M393" t="inlineStr">
         <is>
@@ -40450,7 +40510,11 @@
           <t>Net loss from discontinued operations 5</t>
         </is>
       </c>
-      <c r="D394" t="inlineStr"/>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E394" t="inlineStr">
         <is>
           <t>-</t>
@@ -40477,7 +40541,7 @@
         </is>
       </c>
       <c r="J394" s="5" t="n">
-        <v>0.176</v>
+        <v>-0.176</v>
       </c>
       <c r="K394" t="inlineStr">
         <is>
@@ -42994,7 +43058,11 @@
           <t>Income tax recovery 15</t>
         </is>
       </c>
-      <c r="D424" t="inlineStr"/>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E424" t="inlineStr">
         <is>
           <t>-</t>
@@ -45122,7 +45190,11 @@
           <t>Income tax (recovery) expense 13</t>
         </is>
       </c>
-      <c r="D449" t="inlineStr"/>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E449" t="inlineStr">
         <is>
           <t>-</t>
@@ -45204,7 +45276,11 @@
           <t>Net loss from discontinued operations 2</t>
         </is>
       </c>
-      <c r="D450" t="inlineStr"/>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E450" t="inlineStr">
         <is>
           <t>-</t>
@@ -45221,13 +45297,13 @@
         </is>
       </c>
       <c r="H450" s="5" t="n">
-        <v>3.711</v>
+        <v>-3.711</v>
       </c>
       <c r="I450" s="5" t="n">
-        <v>1.465</v>
+        <v>-1.465</v>
       </c>
       <c r="J450" s="5" t="n">
-        <v>0.176</v>
+        <v>-0.176</v>
       </c>
       <c r="K450" t="inlineStr">
         <is>
@@ -46544,7 +46620,11 @@
           <t>Income tax (recovery) expense 12</t>
         </is>
       </c>
-      <c r="D466" t="inlineStr"/>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E466" t="inlineStr">
         <is>
           <t>-</t>
@@ -48058,7 +48138,11 @@
           <t>Current income tax recovery (expense) (Note 11)</t>
         </is>
       </c>
-      <c r="D484" t="inlineStr"/>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E484" t="inlineStr">
         <is>
           <t>-</t>
@@ -48142,7 +48226,11 @@
           <t>Deferred income tax recovery (expense) (Note 11)</t>
         </is>
       </c>
-      <c r="D485" t="inlineStr"/>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E485" s="5" t="n">
         <v>-0.32977</v>
       </c>
